--- a/fixtures/대진표_예시.xlsx
+++ b/fixtures/대진표_예시.xlsx
@@ -399,17 +399,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E13"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>수준</v>
+        <v>부문</v>
       </c>
       <c r="B1" t="str">
         <v>조</v>
@@ -638,11 +631,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/fixtures/대진표_예시.xlsx
+++ b/fixtures/대진표_예시.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,12 +408,9 @@
         <v>조</v>
       </c>
       <c r="C1" t="str">
-        <v>팀명</v>
+        <v>선수1</v>
       </c>
       <c r="D1" t="str">
-        <v>선수1</v>
-      </c>
-      <c r="E1" t="str">
         <v>선수2</v>
       </c>
     </row>
@@ -425,12 +422,9 @@
         <v>A</v>
       </c>
       <c r="C2" t="str">
-        <v>번개조</v>
+        <v>김철수</v>
       </c>
       <c r="D2" t="str">
-        <v>김철수</v>
-      </c>
-      <c r="E2" t="str">
         <v>이영희</v>
       </c>
     </row>
@@ -442,12 +436,9 @@
         <v>A</v>
       </c>
       <c r="C3" t="str">
-        <v>구름조</v>
+        <v>정다솔</v>
       </c>
       <c r="D3" t="str">
-        <v>정다솔</v>
-      </c>
-      <c r="E3" t="str">
         <v>한가람</v>
       </c>
     </row>
@@ -459,12 +450,9 @@
         <v>A</v>
       </c>
       <c r="C4" t="str">
-        <v>천둥조</v>
+        <v>박민수</v>
       </c>
       <c r="D4" t="str">
-        <v>박민수</v>
-      </c>
-      <c r="E4" t="str">
         <v>최지은</v>
       </c>
     </row>
@@ -476,12 +464,9 @@
         <v>B</v>
       </c>
       <c r="C5" t="str">
-        <v>독수리조</v>
+        <v>이수민</v>
       </c>
       <c r="D5" t="str">
-        <v>이수민</v>
-      </c>
-      <c r="E5" t="str">
         <v>장하나</v>
       </c>
     </row>
@@ -493,12 +478,9 @@
         <v>B</v>
       </c>
       <c r="C6" t="str">
-        <v>매화조</v>
+        <v>오세훈</v>
       </c>
       <c r="D6" t="str">
-        <v>오세훈</v>
-      </c>
-      <c r="E6" t="str">
         <v>윤도현</v>
       </c>
     </row>
@@ -510,12 +492,9 @@
         <v>B</v>
       </c>
       <c r="C7" t="str">
-        <v>소나무조</v>
+        <v>배소연</v>
       </c>
       <c r="D7" t="str">
-        <v>배소연</v>
-      </c>
-      <c r="E7" t="str">
         <v>임재현</v>
       </c>
     </row>
@@ -527,12 +506,9 @@
         <v>A</v>
       </c>
       <c r="C8" t="str">
-        <v>은하수조</v>
+        <v>서지훈</v>
       </c>
       <c r="D8" t="str">
-        <v>서지훈</v>
-      </c>
-      <c r="E8" t="str">
         <v>강나윤</v>
       </c>
     </row>
@@ -544,12 +520,9 @@
         <v>A</v>
       </c>
       <c r="C9" t="str">
-        <v>무지개조</v>
+        <v>홍길동</v>
       </c>
       <c r="D9" t="str">
-        <v>홍길동</v>
-      </c>
-      <c r="E9" t="str">
         <v>성춘향</v>
       </c>
     </row>
@@ -561,12 +534,9 @@
         <v>A</v>
       </c>
       <c r="C10" t="str">
-        <v>단풍조</v>
+        <v>유하은</v>
       </c>
       <c r="D10" t="str">
-        <v>유하은</v>
-      </c>
-      <c r="E10" t="str">
         <v>조민재</v>
       </c>
     </row>
@@ -578,12 +548,9 @@
         <v>B</v>
       </c>
       <c r="C11" t="str">
-        <v>파도조</v>
+        <v>권도윤</v>
       </c>
       <c r="D11" t="str">
-        <v>권도윤</v>
-      </c>
-      <c r="E11" t="str">
         <v>신유나</v>
       </c>
     </row>
@@ -595,12 +562,9 @@
         <v>B</v>
       </c>
       <c r="C12" t="str">
-        <v>별빛조</v>
+        <v>임서준</v>
       </c>
       <c r="D12" t="str">
-        <v>임서준</v>
-      </c>
-      <c r="E12" t="str">
         <v>고은채</v>
       </c>
     </row>
@@ -612,25 +576,22 @@
         <v>B</v>
       </c>
       <c r="C13" t="str">
-        <v>햇살조</v>
+        <v>문지호</v>
       </c>
       <c r="D13" t="str">
-        <v>문지호</v>
-      </c>
-      <c r="E13" t="str">
         <v>백수아</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -645,7 +606,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>수준</v>
+        <v>부문</v>
       </c>
       <c r="B2" t="str">
         <v>대회 부수/레벨 (예: 3.0, 3.5, 4.0)</v>
@@ -659,7 +620,7 @@
         <v>조</v>
       </c>
       <c r="B3" t="str">
-        <v>조별리그 조 이름 (예: A, B, C ...) — 한 수준 안에서 자유롭게 조를 나누면 됩니다</v>
+        <v>조별리그 조 이름 (예: A, B, C ...) — 한 부문 안에서 자유롭게 조를 나누면 됩니다</v>
       </c>
       <c r="C3" t="str">
         <v>필수</v>
@@ -667,10 +628,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>팀명</v>
+        <v>선수1 / 선수2</v>
       </c>
       <c r="B4" t="str">
-        <v>팀 이름</v>
+        <v>팀 선수 이름 (팀명은 별도로 적지 않아도 두 선수 이름으로 자동 생성됩니다)</v>
       </c>
       <c r="C4" t="str">
         <v>필수</v>
@@ -678,21 +639,32 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>선수1 / 선수2</v>
+        <v>■ 이 파일을 업로드하면 자동으로 처리되는 것</v>
       </c>
       <c r="B5" t="str">
-        <v>팀 선수 이름</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>필수</v>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>각 조 안에서 모든 팀이 한 번씩 맞붙는 조별리그 경기가 자동 생성됩니다 (팀 수에 맞춰 라운드 수도 자동 조정).</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>■ 이 파일을 업로드하면 자동으로 처리되는 것</v>
+        <v>2</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>경기 결과가 확정되는 대로 조별 순위(승-패-득실차-맞대결 기준)가 실시간으로 계산됩니다.</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -700,10 +672,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="str">
-        <v>각 조 안에서 모든 팀이 한 번씩 맞붙는 조별리그 경기가 자동 생성됩니다 (팀 수에 맞춰 라운드 수도 자동 조정).</v>
+        <v>각 조의 조별리그 경기가 모두 확정되면, 조 1·2위가 토너먼트 대진에 자동으로 진출합니다 — 버튼을 누를 필요가 없습니다.</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -711,10 +683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="str">
-        <v>경기 결과가 확정되는 대로 조별 순위(승-패-득실차-맞대결 기준)가 실시간으로 계산됩니다.</v>
+        <v>토너먼트 경기 결과가 확정되면 승자가 다음 라운드에 자동으로 올라갑니다 — 더 이상 수동으로 다음 라운드를 입력할 필요가 없습니다.</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -722,10 +694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>3</v>
+        <v>참고</v>
       </c>
       <c r="B10" t="str">
-        <v>조별리그가 끝나면, 관리자 화면(조별 순위)에서 '진출 인원수'를 정하고 버튼을 누르면 토너먼트 대진이 자동 생성됩니다 (인원이 2의 배수가 아니면 부전승도 자동 배정).</v>
+        <v>업로드 시 앱이 팀마다 4자리 코드를 자동으로 발급합니다. 엑셀에 코드를 직접 적을 필요는 없습니다.</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -733,40 +705,18 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>4</v>
+        <v>참고</v>
       </c>
       <c r="B11" t="str">
-        <v>토너먼트 경기 결과가 확정되면 승자가 다음 라운드에 자동으로 올라갑니다 — 더 이상 수동으로 다음 라운드를 입력할 필요가 없습니다.</v>
+        <v>코트 배정은 이 버전에서는 지원하지 않습니다 — 현장에서 관리자가 별도로 안내해주세요.</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>참고</v>
-      </c>
-      <c r="B13" t="str">
-        <v>업로드 시 앱이 팀마다 4자리 코드를 자동으로 발급합니다. 엑셀에 코드를 직접 적을 필요는 없습니다.</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>참고</v>
-      </c>
-      <c r="B14" t="str">
-        <v>코트 배정은 이 버전에서는 지원하지 않습니다 — 현장에서 관리자가 별도로 안내해주세요.</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>